--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1516,7 +1516,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-bilan-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-bilan|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1558,7 +1558,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="perimetre"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1593,7 +1593,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="problematique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="invite"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1663,7 +1663,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="pieceJointe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1699,7 +1699,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="dateProchainBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1731,7 +1731,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
     &lt;code value="synthesePreparationBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1873,7 +1873,7 @@
     <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/output-tddui-task-bilan-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/output-tddui-task-bilan|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.output.value[x]</t>
@@ -1911,7 +1911,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/output-tddui-task-bilan-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/output-tddui-task-bilan"/&gt;
     &lt;code value="syntheseBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1516,7 +1516,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-bilan|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-input-bilan|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1558,7 +1558,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="perimetre"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1593,7 +1593,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="problematique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="invite"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1663,7 +1663,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="pieceJointe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1699,7 +1699,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="dateProchainBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1731,7 +1731,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-bilan"/&gt;
     &lt;code value="synthesePreparationBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1873,7 +1873,7 @@
     <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/output-tddui-task-bilan|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-output-bilan|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.output.value[x]</t>
@@ -1911,7 +1911,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/output-tddui-task-bilan"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-output-bilan"/&gt;
     &lt;code value="syntheseBilan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
